--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="9710" windowHeight="4320"/>
+    <workbookView windowWidth="18350" windowHeight="8000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,93 +26,118 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
-  <si>
-    <t>SL no.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t>Sl no.</t>
   </si>
   <si>
     <t>Keyword</t>
   </si>
   <si>
-    <t>Search volume</t>
-  </si>
-  <si>
-    <t>CPC</t>
-  </si>
-  <si>
-    <t>DA</t>
-  </si>
-  <si>
-    <t>Social site</t>
-  </si>
-  <si>
-    <t>SEO difficulty/KD</t>
-  </si>
-  <si>
-    <t>prompt engineering course bangladesh</t>
-  </si>
-  <si>
-    <t>facebook(1),Youtube(2),Linkedin(1),website(4)</t>
-  </si>
-  <si>
-    <t>prompt engineering training dhaka</t>
-  </si>
-  <si>
-    <t>facebook(1),Youtube(3)website(8)</t>
-  </si>
-  <si>
-    <t>learn prompt engineering bangla</t>
-  </si>
-  <si>
-    <t>Youtube(4),website(6)</t>
-  </si>
-  <si>
-    <t>prompt engineering freelance bd</t>
-  </si>
-  <si>
-    <t>facebook(3),Youtube(4),Linkedin(2),website(6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> chatgpt prompt bangla tutorial</t>
-  </si>
-  <si>
-    <t>facebook(3),Youtube(3),website(4)</t>
-  </si>
-  <si>
-    <t>beginner prompt engineering bd</t>
-  </si>
-  <si>
-    <t>facebook(1),Youtube(4),website(8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ai prompt course dhaka</t>
-  </si>
-  <si>
-    <t>prompt engineering job bangladesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> free prompt engineering bangla</t>
-  </si>
-  <si>
-    <t>nextin prompt engineering</t>
-  </si>
-  <si>
-    <t>==G</t>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Meta discription</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Fule</t>
+  </si>
+  <si>
+    <t>Think the flu is just a "bad cold"? The latest data from the 2024–2025 season indicates otherwise, revealing one of the most severe influenza seasons in recent history.</t>
+  </si>
+  <si>
+    <t>Discover shocking influenza statistics, flu complications, death rates, and why the flu is more dangerous than most people think.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/flu-deadly-influenza-statistics
+</t>
+  </si>
+  <si>
+    <t>Pneumonia</t>
+  </si>
+  <si>
+    <t>From Common Cold to Deadly Pneumonia: The Hidden Causes Doctors Warn About!!</t>
+  </si>
+  <si>
+    <t>Learn what causes pneumonia, early symptoms, risk factors, and how a simple cold can turn into a life-threatening lung infection.</t>
+  </si>
+  <si>
+    <t>/influenza-facts-death-rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cardiovascular Disease</t>
+  </si>
+  <si>
+    <t>Why Diabetic Patients Face Double the Risk of Heart Disease — A Cardiovascular Warning!</t>
+  </si>
+  <si>
+    <t>Explore the link between diabetes and cardiovascular disease, heart attack risk, prevention tips, and how diabetics can protect heart health.</t>
+  </si>
+  <si>
+    <t>/pneumonia-causes-symptoms-risks</t>
+  </si>
+  <si>
+    <t>COVID-19 Pandemic</t>
+  </si>
+  <si>
+    <t>COVID-19 Pandemic: How Politics Shaped Global Decisions and Changed Public Health Forever</t>
+  </si>
+  <si>
+    <t>Understand the benefits of antiviral drugs, when they are needed, how they work, and why they may be essential for family health safety.</t>
+  </si>
+  <si>
+    <t>/diabetes-heart-disease-risk</t>
+  </si>
+  <si>
+    <t>Antiviral Drugs</t>
+  </si>
+  <si>
+    <t>Why Every Household Should Keep Antiviral Drugs: The Essential Protection Guide for Modern Families</t>
+  </si>
+  <si>
+    <t>Examine how political decisions influenced COVID-19 policies, global responses, lockdown strategies, and public health outcomes worldwide.</t>
+  </si>
+  <si>
+    <t>/covid-19-politics-public-health</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,38 +146,53 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="26"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Times New Roman"/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color rgb="FFFFFFFF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color theme="1" tint="0.05"/>
-      <name val="Microsoft YaHei"/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="3" tint="-0.25"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="18"/>
+      <sz val="12"/>
       <color theme="1" tint="0.05"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <sz val="14"/>
+      <color theme="3" tint="-0.25"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1" tint="0.05"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -301,7 +341,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -310,13 +350,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF005884"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46BDC6"/>
+        <fgColor rgb="FF08BCBE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -507,27 +553,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -648,169 +679,190 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1079,55 +1131,17 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="0008BCBE"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>5715</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>582930</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Screenshot 2026-02-25 132622"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13721715" y="6350"/>
-          <a:ext cx="24961215" cy="14011275"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1388,751 +1402,136 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AQ18"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9.09090909090909" customWidth="1"/>
-    <col min="2" max="3" width="32.7272727272727" customWidth="1"/>
-    <col min="4" max="4" width="29.0909090909091" customWidth="1"/>
-    <col min="5" max="5" width="27.2727272727273" customWidth="1"/>
-    <col min="6" max="7" width="32.7272727272727" customWidth="1"/>
+    <col min="2" max="2" width="29.0909090909091" customWidth="1"/>
+    <col min="3" max="3" width="36.3636363636364" customWidth="1"/>
+    <col min="4" max="4" width="45.4545454545455" customWidth="1"/>
+    <col min="5" max="7" width="36.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="100" customHeight="1" spans="1:43">
+    <row r="1" ht="50" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" ht="80" customHeight="1" spans="1:7">
+      <c r="A2" s="4" cm="1">
+        <f t="array" ref="A2:A6">_xlfn.SEQUENCE(5)</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
-      <c r="AN1" s="2"/>
-      <c r="AO1" s="2"/>
-      <c r="AP1" s="2"/>
-      <c r="AQ1" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
-    <row r="2" ht="100" customHeight="1" spans="1:43">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4">
-        <v>320</v>
-      </c>
-      <c r="D2" s="4">
-        <v>0.45</v>
-      </c>
-      <c r="E2" s="4">
-        <v>25</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="4">
+    <row r="3" ht="80" customHeight="1" spans="1:7">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="2"/>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
-    <row r="3" ht="100" customHeight="1" spans="1:43">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4">
-        <v>210</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.38</v>
-      </c>
-      <c r="E3" s="4">
-        <v>28</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="4">
-        <v>10</v>
-      </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="2"/>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="2"/>
-      <c r="AD3" s="2"/>
-      <c r="AE3" s="2"/>
-      <c r="AF3" s="2"/>
-      <c r="AG3" s="2"/>
-      <c r="AH3" s="2"/>
-      <c r="AI3" s="2"/>
-      <c r="AJ3" s="2"/>
-      <c r="AK3" s="2"/>
-      <c r="AL3" s="2"/>
-      <c r="AM3" s="2"/>
-      <c r="AN3" s="2"/>
-      <c r="AO3" s="2"/>
-      <c r="AP3" s="2"/>
-      <c r="AQ3" s="2"/>
+    <row r="4" ht="80" customHeight="1" spans="1:7">
+      <c r="A4" s="12">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
     </row>
-    <row r="4" ht="100" customHeight="1" spans="1:43">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="4">
-        <v>450</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.52</v>
-      </c>
-      <c r="E4" s="4">
+    <row r="5" ht="80" customHeight="1" spans="1:7">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" ht="80" customHeight="1" spans="1:5">
+      <c r="A6" s="12">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="4">
-        <v>15</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="2"/>
-      <c r="AH4" s="2"/>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2"/>
-      <c r="AL4" s="2"/>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
-      <c r="AO4" s="2"/>
-      <c r="AP4" s="2"/>
-      <c r="AQ4" s="2"/>
+      <c r="D6" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="5" ht="100" customHeight="1" spans="1:43">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="4">
-        <v>150</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.29</v>
-      </c>
-      <c r="E5" s="4">
-        <v>30</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="4">
-        <v>8</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="2"/>
-      <c r="AA5" s="2"/>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="2"/>
-      <c r="AE5" s="2"/>
-      <c r="AF5" s="2"/>
-      <c r="AG5" s="2"/>
-      <c r="AH5" s="2"/>
-      <c r="AI5" s="2"/>
-      <c r="AJ5" s="2"/>
-      <c r="AK5" s="2"/>
-      <c r="AL5" s="2"/>
-      <c r="AM5" s="2"/>
-      <c r="AN5" s="2"/>
-      <c r="AO5" s="2"/>
-      <c r="AP5" s="2"/>
-      <c r="AQ5" s="2"/>
+    <row r="7" ht="28.5" spans="1:1">
+      <c r="A7" s="17"/>
     </row>
-    <row r="6" ht="100" customHeight="1" spans="1:43">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="4">
-        <v>280</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.41</v>
-      </c>
-      <c r="E6" s="4">
-        <v>24</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="4">
-        <v>11</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2"/>
-      <c r="AA6" s="2"/>
-      <c r="AB6" s="2"/>
-      <c r="AC6" s="2"/>
-      <c r="AD6" s="2"/>
-      <c r="AE6" s="2"/>
-      <c r="AF6" s="2"/>
-      <c r="AG6" s="2"/>
-      <c r="AH6" s="2"/>
-      <c r="AI6" s="2"/>
-      <c r="AJ6" s="2"/>
-      <c r="AK6" s="2"/>
-      <c r="AL6" s="2"/>
-      <c r="AM6" s="2"/>
-      <c r="AN6" s="2"/>
-      <c r="AO6" s="2"/>
-      <c r="AP6" s="2"/>
-      <c r="AQ6" s="2"/>
-    </row>
-    <row r="7" ht="100" customHeight="1" spans="1:43">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="4">
-        <v>120</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="E7" s="4">
-        <v>26</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="4">
-        <v>7</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="2"/>
-      <c r="AB7" s="2"/>
-      <c r="AC7" s="2"/>
-      <c r="AD7" s="2"/>
-      <c r="AE7" s="2"/>
-      <c r="AF7" s="2"/>
-      <c r="AG7" s="2"/>
-      <c r="AH7" s="2"/>
-      <c r="AI7" s="2"/>
-      <c r="AJ7" s="2"/>
-      <c r="AK7" s="2"/>
-      <c r="AL7" s="2"/>
-      <c r="AM7" s="2"/>
-      <c r="AN7" s="2"/>
-      <c r="AO7" s="2"/>
-      <c r="AP7" s="2"/>
-      <c r="AQ7" s="2"/>
-    </row>
-    <row r="8" ht="100" customHeight="1" spans="1:43">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="4">
-        <v>180</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.35</v>
-      </c>
-      <c r="E8" s="4">
-        <v>27</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="4">
-        <v>9</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="2"/>
-      <c r="AB8" s="2"/>
-      <c r="AC8" s="2"/>
-      <c r="AD8" s="2"/>
-      <c r="AE8" s="2"/>
-      <c r="AF8" s="2"/>
-      <c r="AG8" s="2"/>
-      <c r="AH8" s="2"/>
-      <c r="AI8" s="2"/>
-      <c r="AJ8" s="2"/>
-      <c r="AK8" s="2"/>
-      <c r="AL8" s="2"/>
-      <c r="AM8" s="2"/>
-      <c r="AN8" s="2"/>
-      <c r="AO8" s="2"/>
-      <c r="AP8" s="2"/>
-      <c r="AQ8" s="2"/>
-    </row>
-    <row r="9" ht="100" customHeight="1" spans="1:43">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="4">
-        <v>90</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0.22</v>
-      </c>
-      <c r="E9" s="4">
-        <v>32</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="4">
-        <v>6</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
-      <c r="AA9" s="2"/>
-      <c r="AB9" s="2"/>
-      <c r="AC9" s="2"/>
-      <c r="AD9" s="2"/>
-      <c r="AE9" s="2"/>
-      <c r="AF9" s="2"/>
-      <c r="AG9" s="2"/>
-      <c r="AH9" s="2"/>
-      <c r="AI9" s="2"/>
-      <c r="AJ9" s="2"/>
-      <c r="AK9" s="2"/>
-      <c r="AL9" s="2"/>
-      <c r="AM9" s="2"/>
-      <c r="AN9" s="2"/>
-      <c r="AO9" s="2"/>
-      <c r="AP9" s="2"/>
-      <c r="AQ9" s="2"/>
-    </row>
-    <row r="10" ht="100" customHeight="1" spans="1:43">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="6">
-        <v>350</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0.48</v>
-      </c>
-      <c r="E10" s="6">
-        <v>20</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="6">
-        <v>14</v>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
-      <c r="AB10" s="2"/>
-      <c r="AC10" s="2"/>
-      <c r="AD10" s="2"/>
-      <c r="AE10" s="2"/>
-      <c r="AF10" s="2"/>
-      <c r="AG10" s="2"/>
-      <c r="AH10" s="2"/>
-      <c r="AI10" s="2"/>
-      <c r="AJ10" s="2"/>
-      <c r="AK10" s="2"/>
-      <c r="AL10" s="2"/>
-      <c r="AM10" s="2"/>
-      <c r="AN10" s="2"/>
-      <c r="AO10" s="2"/>
-      <c r="AP10" s="2"/>
-      <c r="AQ10" s="2"/>
-    </row>
-    <row r="11" ht="100" customHeight="1" spans="1:43">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="6">
-        <v>10</v>
-      </c>
-      <c r="D11" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="E11" s="6">
-        <v>15</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="6">
-        <v>2</v>
-      </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2"/>
-      <c r="AB11" s="2"/>
-      <c r="AC11" s="2"/>
-      <c r="AD11" s="2"/>
-      <c r="AE11" s="2"/>
-      <c r="AF11" s="2"/>
-      <c r="AG11" s="2"/>
-      <c r="AH11" s="2"/>
-      <c r="AI11" s="2"/>
-      <c r="AJ11" s="2"/>
-      <c r="AK11" s="2"/>
-      <c r="AL11" s="2"/>
-      <c r="AM11" s="2"/>
-      <c r="AN11" s="2"/>
-      <c r="AO11" s="2"/>
-      <c r="AP11" s="2"/>
-      <c r="AQ11" s="2"/>
-    </row>
-    <row r="12" ht="100" customHeight="1" spans="1:7">
-      <c r="A12" s="3">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" ht="100" customHeight="1" spans="1:24">
-      <c r="A13" s="3">
-        <v>12</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="X13" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" ht="100" customHeight="1" spans="1:7">
-      <c r="A14" s="3">
-        <v>13</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" ht="100" customHeight="1" spans="1:7">
-      <c r="A15" s="3">
-        <v>14</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" ht="100" customHeight="1" spans="1:7">
-      <c r="A16" s="3">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" ht="100" customHeight="1" spans="1:7">
-      <c r="A17" s="3">
-        <v>16</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="18" ht="100" customHeight="1" spans="1:7">
-      <c r="A18" s="8">
-        <v>17</v>
-      </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
+    <row r="8" ht="28.5" spans="1:1">
+      <c r="A8" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H1:AQ11"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>